--- a/food_beverage_order_forms/042_funtastic_giveaway_form--food_beverage_order_forms.xlsx
+++ b/food_beverage_order_forms/042_funtastic_giveaway_form--food_beverage_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Form Phone</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Form Email</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>form_category_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Form Category 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>form_description_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Form Description 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -848,7 +848,7 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
@@ -924,7 +924,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>form_category_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -941,7 +941,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>form_category_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -958,7 +958,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>form_category_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
